--- a/data/proteomics/membrane_size_ratio_across_compartment_NCB.xlsx
+++ b/data/proteomics/membrane_size_ratio_across_compartment_NCB.xlsx
@@ -555,40 +555,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0164927568349891</v>
+        <v>0.01649275683498909</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008208129234940855</v>
+        <v>0.008208129234940862</v>
       </c>
       <c r="E2" t="n">
         <v>0.01048230591661772</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01231301988611195</v>
+        <v>0.01231301988611194</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01388713357267835</v>
+        <v>0.01388713357267836</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009076867394864513</v>
+        <v>0.00907686739486451</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01338302955571036</v>
+        <v>0.01338302955571038</v>
       </c>
       <c r="J2" t="n">
         <v>0.01349924300900982</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01493328544397202</v>
+        <v>0.014933285443972</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009863744799519051</v>
+        <v>0.009863744799519038</v>
       </c>
       <c r="M2" t="n">
         <v>0.01098267902382247</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01094305480355278</v>
+        <v>0.01094305480355277</v>
       </c>
       <c r="O2" t="n">
         <v>0.01139024914590749</v>
@@ -603,22 +603,22 @@
         <v>0.0144366074607466</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01414040837107494</v>
+        <v>0.01414040837107493</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01483999524701294</v>
+        <v>0.01483999524701296</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01653143988585717</v>
+        <v>0.01653143988585719</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01573620194903564</v>
+        <v>0.01573620194903563</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01384238227597991</v>
+        <v>0.01384238227597992</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0137904411002018</v>
+        <v>0.01379044110020178</v>
       </c>
     </row>
     <row r="3">
@@ -631,70 +631,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08224786581142948</v>
+        <v>0.08224786581142947</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08034184083601882</v>
+        <v>0.08034184083601888</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09227702992012664</v>
+        <v>0.09227702992012661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09476756735515926</v>
+        <v>0.09476756735515919</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09412613651901199</v>
+        <v>0.09412613651901205</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08158515031818532</v>
+        <v>0.08158515031818531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09976163266561863</v>
+        <v>0.09976163266561877</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09652711098387147</v>
+        <v>0.09652711098387141</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09864972608956178</v>
+        <v>0.09864972608956174</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06773291537156347</v>
+        <v>0.0677329153715634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07237084465145965</v>
+        <v>0.0723708446514597</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07543275180333839</v>
+        <v>0.07543275180333835</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07825234436443861</v>
+        <v>0.07825234436443863</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06610621328993828</v>
+        <v>0.06610621328993833</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06934300999600081</v>
+        <v>0.06934300999600079</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06963591653814873</v>
+        <v>0.0696359165381487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0608061552928696</v>
+        <v>0.06080615529286958</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06559116018639076</v>
+        <v>0.06559116018639079</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07133468448137406</v>
+        <v>0.07133468448137413</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06990742097850995</v>
+        <v>0.06990742097850992</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0623300369343479</v>
+        <v>0.06233003693434795</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05698948402616182</v>
+        <v>0.05698948402616176</v>
       </c>
     </row>
     <row r="4">
@@ -710,46 +710,46 @@
         <v>0.1419082661009572</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1309500214920456</v>
+        <v>0.1309500214920457</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1135506960302494</v>
+        <v>0.1135506960302495</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1344430092142667</v>
+        <v>0.1344430092142666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1453470050097113</v>
+        <v>0.1453470050097115</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1638746765772831</v>
+        <v>0.163874676577283</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1610104152684645</v>
+        <v>0.1610104152684648</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1755491901160803</v>
+        <v>0.1755491901160802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1541146880049112</v>
+        <v>0.154114688004911</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1153650210192391</v>
+        <v>0.115365021019239</v>
       </c>
       <c r="M4" t="n">
         <v>0.1339689806268724</v>
       </c>
       <c r="N4" t="n">
-        <v>0.148073567975793</v>
+        <v>0.1480735679757929</v>
       </c>
       <c r="O4" t="n">
         <v>0.1469851724254763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1232417189563228</v>
+        <v>0.1232417189563229</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0868956151468987</v>
+        <v>0.08689561514689871</v>
       </c>
       <c r="R4" t="n">
         <v>0.08707497449179365</v>
@@ -758,19 +758,19 @@
         <v>0.1037208248781077</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1370887270655411</v>
+        <v>0.1370887270655412</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1064903624452186</v>
+        <v>0.1064903624452188</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1283727731918437</v>
+        <v>0.1283727731918436</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09450544527295948</v>
+        <v>0.09450544527295958</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1217775660702155</v>
+        <v>0.1217775660702153</v>
       </c>
     </row>
     <row r="5">
@@ -783,46 +783,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1136124121787302</v>
+        <v>0.1136124121787301</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1219656278024497</v>
+        <v>0.1219656278024498</v>
       </c>
       <c r="E5" t="n">
         <v>0.1217285589473931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1100040846286435</v>
+        <v>0.1100040846286434</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1063032240310403</v>
+        <v>0.1063032240310404</v>
       </c>
       <c r="H5" t="n">
         <v>0.1261898544676353</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1133340978149709</v>
+        <v>0.113334097814971</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1050778871535012</v>
+        <v>0.1050778871535011</v>
       </c>
       <c r="K5" t="n">
         <v>0.103013904608125</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1399434826288474</v>
+        <v>0.1399434826288472</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1337805774880486</v>
+        <v>0.1337805774880487</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1232773919875056</v>
+        <v>0.1232773919875055</v>
       </c>
       <c r="O5" t="n">
         <v>0.1252729103502407</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1045517198296523</v>
+        <v>0.1045517198296524</v>
       </c>
       <c r="Q5" t="n">
         <v>0.1132653135756693</v>
@@ -831,22 +831,22 @@
         <v>0.1146848562042305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1184961134243518</v>
+        <v>0.1184961134243517</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1035888492748566</v>
+        <v>0.1035888492748568</v>
       </c>
       <c r="U5" t="n">
-        <v>0.112205281636707</v>
+        <v>0.1122052816367071</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1064275627482173</v>
+        <v>0.1064275627482172</v>
       </c>
       <c r="W5" t="n">
         <v>0.1131161847671158</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1120534969240209</v>
+        <v>0.1120534969240207</v>
       </c>
     </row>
     <row r="6">
@@ -859,70 +859,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0412506988991965</v>
+        <v>0.04125069889919648</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05121736477153627</v>
+        <v>0.0512173647715363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05052066511529828</v>
+        <v>0.05052066511529831</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04380184542170289</v>
+        <v>0.04380184542170286</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03948744740735645</v>
+        <v>0.03948744740735648</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03300435101819546</v>
+        <v>0.03300435101819545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03400781689474693</v>
+        <v>0.03400781689474697</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03240369433357727</v>
+        <v>0.03240369433357726</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03223342576301744</v>
+        <v>0.03223342576301742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05718185535688493</v>
+        <v>0.05718185535688486</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06352836714850893</v>
+        <v>0.06352836714850897</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05954016293170938</v>
+        <v>0.05954016293170934</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06040309415364285</v>
+        <v>0.06040309415364287</v>
       </c>
       <c r="P6" t="n">
-        <v>0.039353982927335</v>
+        <v>0.03935398292733502</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04058925327727624</v>
+        <v>0.04058925327727623</v>
       </c>
       <c r="R6" t="n">
         <v>0.04469854918865443</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04946698576927063</v>
+        <v>0.04946698576927062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03959107613242224</v>
+        <v>0.03959107613242227</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04195371771431004</v>
+        <v>0.04195371771431007</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03875584039016162</v>
+        <v>0.03875584039016159</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04720634246435226</v>
+        <v>0.04720634246435228</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04484991551445998</v>
+        <v>0.04484991551445992</v>
       </c>
     </row>
     <row r="7">
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01413720580352643</v>
+        <v>0.01413720580352642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006535264540196091</v>
+        <v>0.006535264540196097</v>
       </c>
       <c r="E7" t="n">
         <v>0.007485400293390836</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006824141187558664</v>
+        <v>0.00682414118755866</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006872041407501398</v>
+        <v>0.006872041407501404</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007641426373112075</v>
+        <v>0.007641426373112071</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007475025797531669</v>
+        <v>0.007475025797531679</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007268160345577426</v>
+        <v>0.007268160345577424</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007656404706757898</v>
+        <v>0.007656404706757891</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006315095449059733</v>
+        <v>0.006315095449059726</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00634978406569842</v>
+        <v>0.006349784065698424</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006052848184853592</v>
+        <v>0.006052848184853588</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005958793172513994</v>
+        <v>0.005958793172513997</v>
       </c>
       <c r="P7" t="n">
         <v>0.01379118439006075</v>
@@ -983,22 +983,22 @@
         <v>0.009205724369625874</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009118023086125903</v>
+        <v>0.009118023086125899</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008153549255037787</v>
+        <v>0.008153549255037796</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008923711139738652</v>
+        <v>0.008923711139738662</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00861352703209407</v>
+        <v>0.008613527032094059</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008313086995173479</v>
+        <v>0.008313086995173486</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008740914533081604</v>
+        <v>0.008740914533081593</v>
       </c>
     </row>
     <row r="8">
@@ -1011,43 +1011,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01148247137190494</v>
+        <v>0.01148247137190493</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007592132363862214</v>
+        <v>0.00759213236386222</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008768022181645505</v>
+        <v>0.008768022181645506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007760681801067574</v>
+        <v>0.007760681801067568</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007399188349370079</v>
+        <v>0.007399188349370087</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008122056321755439</v>
+        <v>0.008122056321755437</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008087074266578325</v>
+        <v>0.008087074266578335</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007386909544384308</v>
+        <v>0.007386909544384304</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008580510704847097</v>
+        <v>0.008580510704847088</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00908742399372852</v>
+        <v>0.00908742399372851</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007876857788828394</v>
+        <v>0.007876857788828398</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007282592632049696</v>
+        <v>0.007282592632049692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007092662721924181</v>
+        <v>0.007092662721924184</v>
       </c>
       <c r="P8" t="n">
         <v>0.01036268444421098</v>
@@ -1056,25 +1056,25 @@
         <v>0.01002710892261756</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009680602475780783</v>
+        <v>0.009680602475780781</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01034023485232666</v>
+        <v>0.01034023485232665</v>
       </c>
       <c r="T8" t="n">
         <v>0.01056817837701311</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01008085401616031</v>
+        <v>0.01008085401616032</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01116175253713593</v>
+        <v>0.01116175253713592</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009443842668465414</v>
+        <v>0.009443842668465418</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01045002742922933</v>
+        <v>0.01045002742922932</v>
       </c>
     </row>
     <row r="9">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.09534357329876561</v>
+        <v>0.09534357329876554</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1422591370347779</v>
+        <v>0.142259137034778</v>
       </c>
       <c r="E9" t="n">
         <v>0.1350501942264068</v>
@@ -1099,58 +1099,58 @@
         <v>0.1324291244804696</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1332385409277588</v>
+        <v>0.1332385409277589</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1066600918317605</v>
+        <v>0.1066600918317604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1038122231922973</v>
+        <v>0.1038122231922974</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09946936328445917</v>
+        <v>0.09946936328445916</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1099620958393052</v>
+        <v>0.1099620958393051</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09375718933002357</v>
+        <v>0.09375718933002346</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08108758122997507</v>
+        <v>0.08108758122997511</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0806317289780937</v>
+        <v>0.08063172897809365</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07841031685668795</v>
+        <v>0.07841031685668796</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08668973187276842</v>
+        <v>0.08668973187276846</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0966345195975668</v>
+        <v>0.09663451959756682</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09841012546998508</v>
+        <v>0.09841012546998507</v>
       </c>
       <c r="S9" t="n">
         <v>0.1132316224977764</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09124924166658718</v>
+        <v>0.09124924166658727</v>
       </c>
       <c r="U9" t="n">
         <v>0.1003343046969515</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09152760386113032</v>
+        <v>0.09152760386113025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08502957441706607</v>
+        <v>0.08502957441706613</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1023329196255964</v>
+        <v>0.1023329196255963</v>
       </c>
     </row>
     <row r="10">
@@ -1163,40 +1163,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01250218539695481</v>
+        <v>0.0125021853969548</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01191519472490775</v>
+        <v>0.01191519472490776</v>
       </c>
       <c r="E10" t="n">
         <v>0.01137658734118016</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01222938148417079</v>
+        <v>0.01222938148417078</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01251888387357097</v>
+        <v>0.01251888387357099</v>
       </c>
       <c r="H10" t="n">
         <v>0.01339841144510975</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01344775286556709</v>
+        <v>0.01344775286556711</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01294908174638092</v>
+        <v>0.01294908174638091</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01248874270378518</v>
+        <v>0.01248874270378517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01399283037534305</v>
+        <v>0.01399283037534303</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01300440566431079</v>
+        <v>0.0130044056643108</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01191888336333412</v>
+        <v>0.01191888336333411</v>
       </c>
       <c r="O10" t="n">
         <v>0.01164870100019339</v>
@@ -1214,19 +1214,19 @@
         <v>0.01230828062341599</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01135102987027347</v>
+        <v>0.01135102987027348</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01247967398784405</v>
+        <v>0.01247967398784406</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01161589074607085</v>
+        <v>0.01161589074607084</v>
       </c>
       <c r="W10" t="n">
         <v>0.0119214688634799</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01156527400980402</v>
+        <v>0.011565274009804</v>
       </c>
     </row>
     <row r="11">
@@ -1239,40 +1239,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01722116075741057</v>
+        <v>0.01722116075741056</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01486651867067425</v>
+        <v>0.01486651867067427</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01517664597372783</v>
+        <v>0.01517664597372784</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01745364356641511</v>
+        <v>0.0174536435664151</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01694852223270329</v>
+        <v>0.0169485222327033</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0149609653043171</v>
+        <v>0.01496096530431709</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0170629090964607</v>
+        <v>0.01706290909646073</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02025915594515296</v>
+        <v>0.02025915594515295</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01909943035567296</v>
+        <v>0.01909943035567295</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01606436224421408</v>
+        <v>0.01606436224421406</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01802898818017503</v>
+        <v>0.01802898818017504</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01839739860068607</v>
+        <v>0.01839739860068605</v>
       </c>
       <c r="O11" t="n">
         <v>0.01765644875416243</v>
@@ -1281,28 +1281,28 @@
         <v>0.02435137226917222</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02557745841045562</v>
+        <v>0.02557745841045561</v>
       </c>
       <c r="R11" t="n">
         <v>0.02476962168506819</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02501001459722571</v>
+        <v>0.0250100145972257</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03537035528770036</v>
+        <v>0.03537035528770039</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03159286731364031</v>
+        <v>0.03159286731364035</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03468015521471374</v>
+        <v>0.03468015521471371</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02376521365761904</v>
+        <v>0.02376521365761905</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02522728243791856</v>
+        <v>0.02522728243791852</v>
       </c>
     </row>
     <row r="12">
@@ -1315,49 +1315,49 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04668069896037391</v>
+        <v>0.04668069896037387</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04361045428613769</v>
+        <v>0.04361045428613773</v>
       </c>
       <c r="E12" t="n">
         <v>0.04575283956425436</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04462330211594083</v>
+        <v>0.0446233021159408</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04503224502305822</v>
+        <v>0.04503224502305826</v>
       </c>
       <c r="H12" t="n">
         <v>0.03992989133679375</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04833654591562138</v>
+        <v>0.04833654591562143</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05033764478228878</v>
+        <v>0.05033764478228876</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04905400377293285</v>
+        <v>0.04905400377293279</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04872286801401256</v>
+        <v>0.04872286801401251</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05057141743891782</v>
+        <v>0.05057141743891783</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04671485563312121</v>
+        <v>0.04671485563312117</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04933764975127125</v>
+        <v>0.04933764975127124</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04348995993041574</v>
+        <v>0.04348995993041576</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.04546443867139097</v>
+        <v>0.04546443867139095</v>
       </c>
       <c r="R12" t="n">
         <v>0.04470261946993318</v>
@@ -1366,19 +1366,19 @@
         <v>0.04627303446890788</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06965457467090144</v>
+        <v>0.0696545746709015</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06773448788794979</v>
+        <v>0.06773448788794986</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07002415471581977</v>
+        <v>0.0700241547158197</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04569539001439133</v>
+        <v>0.04569539001439137</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04965759928454555</v>
+        <v>0.04965759928454549</v>
       </c>
     </row>
     <row r="13">
@@ -1391,70 +1391,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02576412629457496</v>
+        <v>0.02576412629457494</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01997722259698072</v>
+        <v>0.01997722259698073</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0218478061691171</v>
+        <v>0.02184780616911711</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02341317934908384</v>
+        <v>0.02341317934908383</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02442199123470916</v>
+        <v>0.02442199123470918</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01902657621422252</v>
+        <v>0.01902657621422251</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02138058665564797</v>
+        <v>0.02138058665564799</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02184946799987173</v>
+        <v>0.02184946799987172</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02424626882924052</v>
+        <v>0.0242462688292405</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03149777585691258</v>
+        <v>0.03149777585691255</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03311064353981588</v>
+        <v>0.0331106435398159</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03393668817963873</v>
+        <v>0.0339366881796387</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03378531125881964</v>
+        <v>0.03378531125881966</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03893970869156921</v>
+        <v>0.03893970869156923</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04220865882736152</v>
+        <v>0.0422086588273615</v>
       </c>
       <c r="R13" t="n">
         <v>0.04361119177246294</v>
       </c>
       <c r="S13" t="n">
-        <v>0.04081604649730005</v>
+        <v>0.04081604649730002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02913842843091857</v>
+        <v>0.02913842843091859</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03252386728233981</v>
+        <v>0.03252386728233984</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02967582521734906</v>
+        <v>0.02967582521734903</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04524188887875064</v>
+        <v>0.04524188887875067</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04104168245356081</v>
+        <v>0.04104168245356076</v>
       </c>
     </row>
     <row r="14">
@@ -1467,70 +1467,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.008622615405933934</v>
+        <v>0.008622615405933929</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006795540529737302</v>
+        <v>0.006795540529737309</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008144352492360148</v>
+        <v>0.008144352492360151</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006887266904530526</v>
+        <v>0.006887266904530518</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006897947503075819</v>
+        <v>0.006897947503075826</v>
       </c>
       <c r="H14" t="n">
-        <v>0.007161428816046707</v>
+        <v>0.007161428816046705</v>
       </c>
       <c r="I14" t="n">
-        <v>0.007913043389076989</v>
+        <v>0.007913043389077001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00933467947102873</v>
+        <v>0.009334679471028725</v>
       </c>
       <c r="K14" t="n">
-        <v>0.009058409345385559</v>
+        <v>0.009058409345385552</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007857898324793267</v>
+        <v>0.007857898324793259</v>
       </c>
       <c r="M14" t="n">
-        <v>0.007820064566437003</v>
+        <v>0.007820064566437007</v>
       </c>
       <c r="N14" t="n">
-        <v>0.007634418264762018</v>
+        <v>0.007634418264762014</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007327798016857914</v>
+        <v>0.007327798016857917</v>
       </c>
       <c r="P14" t="n">
-        <v>0.007883313795333462</v>
+        <v>0.007883313795333467</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.005299294277038436</v>
+        <v>0.005299294277038435</v>
       </c>
       <c r="R14" t="n">
-        <v>0.005270569382237314</v>
+        <v>0.005270569382237313</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005072585909439237</v>
+        <v>0.005072585909439234</v>
       </c>
       <c r="T14" t="n">
-        <v>0.005080637580088085</v>
+        <v>0.005080637580088089</v>
       </c>
       <c r="U14" t="n">
-        <v>0.005609567568547615</v>
+        <v>0.00560956756854762</v>
       </c>
       <c r="V14" t="n">
-        <v>0.00534119943863882</v>
+        <v>0.005341199438638816</v>
       </c>
       <c r="W14" t="n">
-        <v>0.005049941303751805</v>
+        <v>0.005049941303751807</v>
       </c>
       <c r="X14" t="n">
-        <v>0.005062426770605481</v>
+        <v>0.005062426770605474</v>
       </c>
     </row>
     <row r="15">
@@ -1543,70 +1543,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.08479917010200291</v>
+        <v>0.08479917010200289</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07153964235261635</v>
+        <v>0.07153964235261642</v>
       </c>
       <c r="E15" t="n">
         <v>0.06807666446817232</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08682424661490476</v>
+        <v>0.08682424661490466</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1120332169695862</v>
+        <v>0.1120332169695863</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06899049390013673</v>
+        <v>0.0689904939001367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1224818895945969</v>
+        <v>0.122481889594597</v>
       </c>
       <c r="J15" t="n">
         <v>0.1148550287860105</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1118584289148088</v>
+        <v>0.1118584289148086</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07265574820082188</v>
+        <v>0.07265574820082181</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08835902634531302</v>
+        <v>0.08835902634531306</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09788915833592776</v>
+        <v>0.09788915833592766</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1032378757494446</v>
+        <v>0.1032378757494447</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0728034979687405</v>
+        <v>0.07280349796874051</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.08115124243059961</v>
+        <v>0.0811512424305996</v>
       </c>
       <c r="R15" t="n">
         <v>0.08405584659936927</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0878389438440927</v>
+        <v>0.08783894384409266</v>
       </c>
       <c r="T15" t="n">
         <v>0.1162944552481207</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09861905138338549</v>
+        <v>0.0986190513833856</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1111207466054336</v>
+        <v>0.1111207466054335</v>
       </c>
       <c r="W15" t="n">
-        <v>0.08099357513605505</v>
+        <v>0.0809935751360551</v>
       </c>
       <c r="X15" t="n">
-        <v>0.09413507477726592</v>
+        <v>0.09413507477726582</v>
       </c>
     </row>
     <row r="16">
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000735439777535953</v>
+        <v>0.0007354397775359527</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001944995867000542</v>
+        <v>0.0001944995867000544</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001908425834722296</v>
+        <v>0.0001908425834722297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002167711151046446</v>
+        <v>0.0002167711151046444</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002029872987362627</v>
+        <v>0.0002029872987362629</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002697390746942267</v>
+        <v>0.0002697390746942266</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000244667163812346</v>
+        <v>0.0002446671638123463</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002011281482946805</v>
+        <v>0.0002011281482946804</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0002141304165929704</v>
+        <v>0.0002141304165929702</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002240104053784125</v>
+        <v>0.0002240104053784122</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0002029031610606185</v>
+        <v>0.0002029031610606186</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001724382542603215</v>
+        <v>0.0001724382542603214</v>
       </c>
       <c r="O16" t="n">
         <v>0.0001502509254140402</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0005004651504809954</v>
+        <v>0.0005004651504809955</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0001018331694808497</v>
@@ -1667,22 +1667,22 @@
         <v>0.0001040547291898317</v>
       </c>
       <c r="S16" t="n">
-        <v>8.657513509789757e-05</v>
+        <v>8.657513509789753e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>8.79558249013555e-05</v>
+        <v>8.795582490135558e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>9.544544988458677e-05</v>
+        <v>9.544544988458686e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>9.022286172319268e-05</v>
+        <v>9.022286172319262e-05</v>
       </c>
       <c r="W16" t="n">
         <v>0.0001009373577160974</v>
       </c>
       <c r="X16" t="n">
-        <v>8.932725190556116e-05</v>
+        <v>8.932725190556106e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1707,28 +1707,28 @@
         <v>0.01396108838253305</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01438827203093771</v>
+        <v>0.01438827203093772</v>
       </c>
       <c r="H17" t="n">
         <v>0.01150678765713455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0141178718132912</v>
+        <v>0.01411787181329121</v>
       </c>
       <c r="J17" t="n">
         <v>0.014277861856785</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01434781607572553</v>
+        <v>0.01434781607572551</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01213566741313523</v>
+        <v>0.01213566741313522</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01241256306453744</v>
+        <v>0.01241256306453745</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0124715331621098</v>
+        <v>0.01247153316210979</v>
       </c>
       <c r="O17" t="n">
         <v>0.01303160418394165</v>
@@ -1740,25 +1740,25 @@
         <v>0.0145145632442422</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01299644138140426</v>
+        <v>0.01299644138140425</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01286834926295572</v>
+        <v>0.01286834926295571</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01413613038284149</v>
+        <v>0.0141361303828415</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01549168207543266</v>
+        <v>0.01549168207543268</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01443759986127728</v>
+        <v>0.01443759986127726</v>
       </c>
       <c r="W17" t="n">
         <v>0.01310278811756955</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01321583655132416</v>
+        <v>0.01321583655132415</v>
       </c>
     </row>
     <row r="18">
@@ -1771,70 +1771,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008658534848189242</v>
+        <v>0.0008658534848189238</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000234269787060309</v>
+        <v>0.0002342697870603092</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003986858707751768</v>
+        <v>0.0003986858707751769</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0002861312388995959</v>
+        <v>0.0002861312388995957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002809838648186899</v>
+        <v>0.0002809838648186901</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0003384097707178017</v>
+        <v>0.0003384097707178016</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0002379017131149786</v>
+        <v>0.0002379017131149789</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0002589110501078883</v>
+        <v>0.0002589110501078882</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0003515774550187646</v>
+        <v>0.0003515774550187643</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0003058309989347252</v>
+        <v>0.0003058309989347249</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0002603112602283895</v>
+        <v>0.0002603112602283896</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0002837793655374178</v>
+        <v>0.0002837793655374176</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0002713035987420739</v>
+        <v>0.000271303598742074</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0006055481344412458</v>
+        <v>0.000605548134441246</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0002489864256117169</v>
+        <v>0.0002489864256117168</v>
       </c>
       <c r="R18" t="n">
         <v>0.0002211626194413561</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002051126344108818</v>
+        <v>0.0002051126344108817</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0001972933393370096</v>
+        <v>0.0001972933393370098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0002185204195525981</v>
+        <v>0.0002185204195525984</v>
       </c>
       <c r="V18" t="n">
-        <v>0.000180211583480253</v>
+        <v>0.0001802115834802528</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0002066060443644719</v>
+        <v>0.000206606044364472</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0002068479703882454</v>
+        <v>0.0002068479703882452</v>
       </c>
     </row>
     <row r="19">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001330544200296793</v>
+        <v>0.001330544200296792</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0009372377425797228</v>
+        <v>0.0009372377425797237</v>
       </c>
       <c r="E19" t="n">
         <v>0.001045823423029261</v>
@@ -1859,58 +1859,58 @@
         <v>0.001113040881798374</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0008657686775820433</v>
+        <v>0.000865768677582044</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001106419547280267</v>
+        <v>0.001106419547280266</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0009538337550794438</v>
+        <v>0.0009538337550794451</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001167993731927647</v>
+        <v>0.001167993731927646</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001019485469366628</v>
+        <v>0.001019485469366627</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0009217811007900439</v>
+        <v>0.0009217811007900429</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001155412990399923</v>
+        <v>0.001155412990399924</v>
       </c>
       <c r="N19" t="n">
-        <v>0.001100006717832776</v>
+        <v>0.001100006717832775</v>
       </c>
       <c r="O19" t="n">
         <v>0.001112352616572833</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0008964948237215245</v>
+        <v>0.0008964948237215249</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0006095608624161838</v>
+        <v>0.0006095608624161837</v>
       </c>
       <c r="R19" t="n">
         <v>0.0005550619086416288</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0008075484323694268</v>
+        <v>0.0008075484323694264</v>
       </c>
       <c r="T19" t="n">
-        <v>0.001044481941877802</v>
+        <v>0.001044481941877803</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0006786601910093847</v>
+        <v>0.0006786601910093855</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0009785328264912798</v>
+        <v>0.0009785328264912789</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0007240766846966573</v>
+        <v>0.0007240766846966576</v>
       </c>
       <c r="X19" t="n">
-        <v>0.001189006841793489</v>
+        <v>0.001189006841793488</v>
       </c>
     </row>
     <row r="20">
@@ -1923,70 +1923,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001911750939613596</v>
+        <v>0.001911750939613595</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001237069237755789</v>
+        <v>0.00123706923775579</v>
       </c>
       <c r="E20" t="n">
         <v>0.001282989959213689</v>
       </c>
       <c r="F20" t="n">
-        <v>0.001176185261971151</v>
+        <v>0.00117618526197115</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001216243150240309</v>
+        <v>0.001216243150240311</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0014614220197122</v>
+        <v>0.001461422019712199</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001337347920052535</v>
+        <v>0.001337347920052537</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001266834510279055</v>
+        <v>0.001266834510279054</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0013288052722921</v>
+        <v>0.001328805272292099</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003188221817828382</v>
+        <v>0.003188221817828379</v>
       </c>
       <c r="M20" t="n">
-        <v>0.003555563969099395</v>
+        <v>0.003555563969099397</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003676253108552227</v>
+        <v>0.003676253108552224</v>
       </c>
       <c r="O20" t="n">
-        <v>0.003239341572514465</v>
+        <v>0.003239341572514466</v>
       </c>
       <c r="P20" t="n">
-        <v>0.002900977005458849</v>
+        <v>0.002900977005458851</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.002630503710220638</v>
+        <v>0.002630503710220637</v>
       </c>
       <c r="R20" t="n">
         <v>0.002946182351239912</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0043772742981628</v>
+        <v>0.004377274298162798</v>
       </c>
       <c r="T20" t="n">
-        <v>0.002824385868327169</v>
+        <v>0.002824385868327171</v>
       </c>
       <c r="U20" t="n">
-        <v>0.003421185878112198</v>
+        <v>0.003421185878112201</v>
       </c>
       <c r="V20" t="n">
-        <v>0.003290510347339346</v>
+        <v>0.003290510347339343</v>
       </c>
       <c r="W20" t="n">
-        <v>0.00465431079146409</v>
+        <v>0.004654310791464093</v>
       </c>
       <c r="X20" t="n">
-        <v>0.003889525314529967</v>
+        <v>0.003889525314529962</v>
       </c>
     </row>
     <row r="21">
@@ -2002,43 +2002,43 @@
         <v>0.01106233828493631</v>
       </c>
       <c r="D21" t="n">
-        <v>0.009924940045223483</v>
+        <v>0.009924940045223492</v>
       </c>
       <c r="E21" t="n">
         <v>0.01249078900606083</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01377575239532274</v>
+        <v>0.01377575239532273</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01413242855621677</v>
+        <v>0.01413242855621678</v>
       </c>
       <c r="H21" t="n">
-        <v>0.007729882707388485</v>
+        <v>0.007729882707388482</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01148592745540468</v>
+        <v>0.0114859274554047</v>
       </c>
       <c r="J21" t="n">
         <v>0.0116559216551766</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01236879773419063</v>
+        <v>0.01236879773419062</v>
       </c>
       <c r="L21" t="n">
-        <v>0.009972396344529703</v>
+        <v>0.009972396344529693</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01159062159284685</v>
+        <v>0.01159062159284686</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01261749504245767</v>
+        <v>0.01261749504245766</v>
       </c>
       <c r="O21" t="n">
         <v>0.01294616292042673</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01194905802614693</v>
+        <v>0.01194905802614694</v>
       </c>
       <c r="Q21" t="n">
         <v>0.01455938064257637</v>
@@ -2047,22 +2047,22 @@
         <v>0.01432699663797069</v>
       </c>
       <c r="S21" t="n">
-        <v>0.01281839489323424</v>
+        <v>0.01281839489323423</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01439815842948827</v>
+        <v>0.01439815842948829</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01514519719286928</v>
+        <v>0.01514519719286929</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01473284922596553</v>
+        <v>0.01473284922596551</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01313116534043713</v>
+        <v>0.01313116534043714</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0126008359480992</v>
+        <v>0.01260083594809919</v>
       </c>
     </row>
     <row r="22">
@@ -2075,70 +2075,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001105544763003308</v>
+        <v>0.001105544763003307</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0007177039225825495</v>
+        <v>0.0007177039225825502</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0009033284481480326</v>
+        <v>0.0009033284481480327</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0008849400568485556</v>
+        <v>0.0008849400568485547</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0007708688302656866</v>
+        <v>0.0007708688302656872</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0009781355664350256</v>
+        <v>0.0009781355664350254</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0007484791905280657</v>
+        <v>0.0007484791905280668</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0008633869688061953</v>
+        <v>0.0008633869688061949</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0009100037110316498</v>
+        <v>0.0009100037110316491</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0007607762389282237</v>
+        <v>0.0007607762389282228</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0008732297083925804</v>
+        <v>0.0008732297083925809</v>
       </c>
       <c r="N22" t="n">
-        <v>0.000783657355146527</v>
+        <v>0.0007836573551465264</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0007565677193281128</v>
+        <v>0.0007565677193281132</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0009685608703840874</v>
+        <v>0.0009685608703840876</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0002280981898907257</v>
+        <v>0.0002280981898907256</v>
       </c>
       <c r="R22" t="n">
         <v>0.0001734303030396737</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0001818934236281929</v>
+        <v>0.0001818934236281928</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0001812359658283173</v>
+        <v>0.0001812359658283175</v>
       </c>
       <c r="U22" t="n">
-        <v>0.000212978647716065</v>
+        <v>0.0002129786477160652</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0002489685313948415</v>
+        <v>0.0002489685313948413</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0002061257118704059</v>
+        <v>0.000206125711870406</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0001970878524305524</v>
+        <v>0.0001970878524305522</v>
       </c>
     </row>
     <row r="23">
@@ -2151,40 +2151,40 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02052240307775973</v>
+        <v>0.02052240307775972</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01947773029109229</v>
+        <v>0.01947773029109231</v>
       </c>
       <c r="E23" t="n">
         <v>0.02448957680826372</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02400317896509873</v>
+        <v>0.02400317896509871</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02462328519210668</v>
+        <v>0.0246232851921067</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0196389399913286</v>
+        <v>0.01963893999132859</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02618126413377425</v>
+        <v>0.02618126413377429</v>
       </c>
       <c r="J23" t="n">
-        <v>0.02535293264780038</v>
+        <v>0.02535293264780037</v>
       </c>
       <c r="K23" t="n">
-        <v>0.02726852255944909</v>
+        <v>0.02726852255944906</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01558677647555022</v>
+        <v>0.01558677647555021</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01845383966298602</v>
+        <v>0.01845383966298603</v>
       </c>
       <c r="N23" t="n">
-        <v>0.02002873232778411</v>
+        <v>0.02002873232778409</v>
       </c>
       <c r="O23" t="n">
         <v>0.02106673689568196</v>
@@ -2199,22 +2199,22 @@
         <v>0.02077148868214098</v>
       </c>
       <c r="S23" t="n">
-        <v>0.01714882066139059</v>
+        <v>0.01714882066139058</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01938877525915688</v>
+        <v>0.01938877525915689</v>
       </c>
       <c r="U23" t="n">
-        <v>0.02088909752829558</v>
+        <v>0.0208890975282956</v>
       </c>
       <c r="V23" t="n">
-        <v>0.02065452803298767</v>
+        <v>0.02065452803298765</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0174950670036655</v>
+        <v>0.01749506700366551</v>
       </c>
       <c r="X23" t="n">
-        <v>0.01622938567012534</v>
+        <v>0.01622938567012532</v>
       </c>
     </row>
     <row r="24">
@@ -2227,40 +2227,40 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.006360510319776176</v>
+        <v>0.006360510319776173</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0008951325744610744</v>
+        <v>0.0008951325744610752</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0007059140636677335</v>
+        <v>0.0007059140636677336</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0015273459044074</v>
+        <v>0.001527345904407399</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001501044249700215</v>
+        <v>0.001501044249700216</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01168094780375174</v>
+        <v>0.01168094780375173</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01072510909189629</v>
+        <v>0.01072510909189631</v>
       </c>
       <c r="J24" t="n">
         <v>0.01518962925871231</v>
       </c>
       <c r="K24" t="n">
-        <v>0.007428703613142936</v>
+        <v>0.007428703613142929</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001164092219370153</v>
+        <v>0.001164092219370152</v>
       </c>
       <c r="M24" t="n">
-        <v>0.001879955140099634</v>
+        <v>0.001879955140099635</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001955637871465994</v>
+        <v>0.001955637871465993</v>
       </c>
       <c r="O24" t="n">
         <v>0.001630496686639974</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005537354377199141</v>
+        <v>0.000553735437719914</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.0003887772947458119</v>
+        <v>0.000388777294745812</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003758137196337047</v>
+        <v>0.0003758137196337045</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2341,28 +2341,28 @@
         <v>0.0006661275110652986</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0005502544526794052</v>
+        <v>0.000550254452679405</v>
       </c>
       <c r="R26" t="n">
         <v>0.0004623770555882961</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004584515972247753</v>
+        <v>0.0004584515972247751</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0003516300009279806</v>
+        <v>0.000351630000927981</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0004612286530068907</v>
+        <v>0.0004612286530068912</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0003829341994870543</v>
+        <v>0.000382934199487054</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0004547703462742863</v>
+        <v>0.0004547703462742865</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0004740209273459054</v>
+        <v>0.0004740209273459048</v>
       </c>
     </row>
     <row r="27">
@@ -2375,70 +2375,70 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.00197312842234976</v>
+        <v>0.001973128422349758</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0008788376512793249</v>
+        <v>0.0008788376512793258</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000963998349363155</v>
+        <v>0.0009639983493631551</v>
       </c>
       <c r="F27" t="n">
-        <v>0.000893146181184378</v>
+        <v>0.0008931461811843773</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0008947553074415363</v>
+        <v>0.0008947553074415371</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0008559163925711062</v>
+        <v>0.0008559163925711059</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0008280852385490353</v>
+        <v>0.0008280852385490365</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0008215701110158118</v>
+        <v>0.0008215701110158114</v>
       </c>
       <c r="K27" t="n">
-        <v>0.000944531286539903</v>
+        <v>0.0009445312865399021</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001439755920822498</v>
+        <v>0.001439755920822497</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001299927072437727</v>
+        <v>0.001299927072437728</v>
       </c>
       <c r="N27" t="n">
         <v>0.001026937176824651</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0009279782260426971</v>
+        <v>0.0009279782260426973</v>
       </c>
       <c r="P27" t="n">
-        <v>0.001745161770501921</v>
+        <v>0.001745161770501922</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0009896667004415784</v>
+        <v>0.0009896667004415782</v>
       </c>
       <c r="R27" t="n">
         <v>0.001057202110208995</v>
       </c>
       <c r="S27" t="n">
-        <v>0.001129556486422044</v>
+        <v>0.001129556486422043</v>
       </c>
       <c r="T27" t="n">
         <v>0.001093638316878569</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0009595151947975926</v>
+        <v>0.0009595151947975936</v>
       </c>
       <c r="V27" t="n">
-        <v>0.000952578491428211</v>
+        <v>0.0009525784914282102</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001037974107282685</v>
+        <v>0.001037974107282686</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001042969048294473</v>
+        <v>0.001042969048294472</v>
       </c>
     </row>
     <row r="28">
@@ -2451,70 +2451,70 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001100961383377168</v>
+        <v>0.001100961383377167</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0004793099703279766</v>
+        <v>0.0004793099703279771</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0005568047878056657</v>
+        <v>0.0005568047878056658</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0004782077417952106</v>
+        <v>0.0004782077417952102</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0003841429696879584</v>
+        <v>0.0003841429696879587</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0007011230676073988</v>
+        <v>0.0007011230676073986</v>
       </c>
       <c r="I28" t="n">
-        <v>0.000563270267776378</v>
+        <v>0.0005632702677763788</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0005514013026690799</v>
+        <v>0.0005514013026690797</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000474047567257281</v>
+        <v>0.0004740475672572806</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0008653120882007012</v>
+        <v>0.0008653120882007002</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0007839911573053471</v>
+        <v>0.0007839911573053475</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0008318713532343451</v>
+        <v>0.0008318713532343444</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0007224768222100574</v>
+        <v>0.0007224768222100576</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0009599650437257744</v>
+        <v>0.0009599650437257749</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0005714038287386486</v>
+        <v>0.0005714038287386485</v>
       </c>
       <c r="R28" t="n">
         <v>0.0005006385393837711</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0005132647085655548</v>
+        <v>0.0005132647085655546</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0002837930592886614</v>
+        <v>0.0002837930592886617</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0003928565714838072</v>
+        <v>0.0003928565714838076</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0004303745034124463</v>
+        <v>0.0004303745034124459</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0006030855692273615</v>
+        <v>0.0006030855692273618</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0006465105148829992</v>
+        <v>0.0006465105148829984</v>
       </c>
     </row>
     <row r="29">
@@ -2527,46 +2527,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002513837612773814</v>
+        <v>0.002513837612773812</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0007867200957786448</v>
+        <v>0.0007867200957786455</v>
       </c>
       <c r="E29" t="n">
         <v>0.001098855638402761</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0009777590996853714</v>
+        <v>0.0009777590996853706</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0009516364247912471</v>
+        <v>0.0009516364247912478</v>
       </c>
       <c r="H29" t="n">
         <v>0.001049887541526182</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0008326018613059097</v>
+        <v>0.0008326018613059108</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0008469109570473409</v>
+        <v>0.0008469109570473406</v>
       </c>
       <c r="K29" t="n">
-        <v>0.001046398783199471</v>
+        <v>0.00104639878319947</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0007435593109133375</v>
+        <v>0.0007435593109133366</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0007358051466481977</v>
+        <v>0.0007358051466481981</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0008894383603805693</v>
+        <v>0.0008894383603805688</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0008942533075025978</v>
+        <v>0.0008942533075025981</v>
       </c>
       <c r="P29" t="n">
-        <v>0.003414083024796727</v>
+        <v>0.003414083024796728</v>
       </c>
       <c r="Q29" t="n">
         <v>0.00151432679492438</v>
@@ -2575,22 +2575,22 @@
         <v>0.001486198485600465</v>
       </c>
       <c r="S29" t="n">
-        <v>0.001353578514857659</v>
+        <v>0.001353578514857658</v>
       </c>
       <c r="T29" t="n">
-        <v>0.001163270255443036</v>
+        <v>0.001163270255443037</v>
       </c>
       <c r="U29" t="n">
-        <v>0.001346540049345189</v>
+        <v>0.001346540049345191</v>
       </c>
       <c r="V29" t="n">
-        <v>0.001523386130479407</v>
+        <v>0.001523386130479406</v>
       </c>
       <c r="W29" t="n">
-        <v>0.001571434316137862</v>
+        <v>0.001571434316137863</v>
       </c>
       <c r="X29" t="n">
-        <v>0.00198032775810542</v>
+        <v>0.001980327758105417</v>
       </c>
     </row>
     <row r="30">
@@ -2603,40 +2603,40 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001907648362113465</v>
+        <v>0.001907648362113464</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001451439943047209</v>
+        <v>0.00145143994304721</v>
       </c>
       <c r="E30" t="n">
         <v>0.00191734279622672</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001690888942175878</v>
+        <v>0.001690888942175877</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001672613113161815</v>
+        <v>0.001672613113161816</v>
       </c>
       <c r="H30" t="n">
-        <v>0.001762189586745996</v>
+        <v>0.001762189586745995</v>
       </c>
       <c r="I30" t="n">
-        <v>0.001588614289658985</v>
+        <v>0.001588614289658987</v>
       </c>
       <c r="J30" t="n">
-        <v>0.001647092595387052</v>
+        <v>0.001647092595387051</v>
       </c>
       <c r="K30" t="n">
-        <v>0.001869127759989151</v>
+        <v>0.001869127759989149</v>
       </c>
       <c r="L30" t="n">
-        <v>0.001697143670566</v>
+        <v>0.001697143670565998</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001680594661820025</v>
+        <v>0.001680594661820026</v>
       </c>
       <c r="N30" t="n">
-        <v>0.001751717832684882</v>
+        <v>0.001751717832684881</v>
       </c>
       <c r="O30" t="n">
         <v>0.001668373528989313</v>
@@ -2654,10 +2654,10 @@
         <v>0.001161850589461504</v>
       </c>
       <c r="T30" t="n">
-        <v>0.001028770903204091</v>
+        <v>0.001028770903204092</v>
       </c>
       <c r="U30" t="n">
-        <v>0.001126641339488815</v>
+        <v>0.001126641339488816</v>
       </c>
       <c r="V30" t="n">
         <v>0.001098149190636439</v>
@@ -2666,7 +2666,7 @@
         <v>0.001206035298283133</v>
       </c>
       <c r="X30" t="n">
-        <v>0.001275766770761885</v>
+        <v>0.001275766770761884</v>
       </c>
     </row>
     <row r="31">
@@ -2679,70 +2679,70 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.004142951826233519</v>
+        <v>0.004142951826233517</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003994463782941898</v>
+        <v>0.003994463782941902</v>
       </c>
       <c r="E31" t="n">
         <v>0.00551732182864048</v>
       </c>
       <c r="F31" t="n">
-        <v>0.004993476511937171</v>
+        <v>0.004993476511937167</v>
       </c>
       <c r="G31" t="n">
-        <v>0.005240103438396935</v>
+        <v>0.00524010343839694</v>
       </c>
       <c r="H31" t="n">
-        <v>0.005789664365831414</v>
+        <v>0.005789664365831412</v>
       </c>
       <c r="I31" t="n">
-        <v>0.004251995070345876</v>
+        <v>0.004251995070345882</v>
       </c>
       <c r="J31" t="n">
-        <v>0.004291419770100875</v>
+        <v>0.004291419770100873</v>
       </c>
       <c r="K31" t="n">
-        <v>0.004740363874916192</v>
+        <v>0.004740363874916188</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00286509843936762</v>
+        <v>0.002865098439367617</v>
       </c>
       <c r="M31" t="n">
-        <v>0.003718830358349219</v>
+        <v>0.003718830358349221</v>
       </c>
       <c r="N31" t="n">
-        <v>0.003788642172734647</v>
+        <v>0.003788642172734644</v>
       </c>
       <c r="O31" t="n">
-        <v>0.003305930504225074</v>
+        <v>0.003305930504225075</v>
       </c>
       <c r="P31" t="n">
-        <v>0.003392721565024639</v>
+        <v>0.00339272156502464</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.004035277679791934</v>
+        <v>0.004035277679791933</v>
       </c>
       <c r="R31" t="n">
         <v>0.00393367086734082</v>
       </c>
       <c r="S31" t="n">
-        <v>0.003127937383662278</v>
+        <v>0.003127937383662276</v>
       </c>
       <c r="T31" t="n">
-        <v>0.003985638790179706</v>
+        <v>0.00398563879017971</v>
       </c>
       <c r="U31" t="n">
-        <v>0.004575093490172022</v>
+        <v>0.004575093490172027</v>
       </c>
       <c r="V31" t="n">
-        <v>0.004717371387332911</v>
+        <v>0.004717371387332908</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003975728555249464</v>
+        <v>0.003975728555249466</v>
       </c>
       <c r="X31" t="n">
-        <v>0.003250892254685793</v>
+        <v>0.003250892254685789</v>
       </c>
     </row>
     <row r="32">
@@ -2755,70 +2755,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.004795770900806151</v>
+        <v>0.004795770900806148</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00362301596910995</v>
+        <v>0.003623015969109953</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002978695434897748</v>
+        <v>0.002978695434897749</v>
       </c>
       <c r="F32" t="n">
-        <v>0.004319197695602904</v>
+        <v>0.0043191976956029</v>
       </c>
       <c r="G32" t="n">
-        <v>0.004033880228799359</v>
+        <v>0.004033880228799362</v>
       </c>
       <c r="H32" t="n">
-        <v>0.002740390775149688</v>
+        <v>0.002740390775149686</v>
       </c>
       <c r="I32" t="n">
-        <v>0.00332545045889683</v>
+        <v>0.003325450458896834</v>
       </c>
       <c r="J32" t="n">
-        <v>0.005786446588098581</v>
+        <v>0.005786446588098578</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005804896442243154</v>
+        <v>0.005804896442243149</v>
       </c>
       <c r="L32" t="n">
-        <v>0.003508940984075159</v>
+        <v>0.003508940984075155</v>
       </c>
       <c r="M32" t="n">
-        <v>0.005083320440404025</v>
+        <v>0.005083320440404028</v>
       </c>
       <c r="N32" t="n">
-        <v>0.005491679099996904</v>
+        <v>0.005491679099996901</v>
       </c>
       <c r="O32" t="n">
-        <v>0.005294444836375531</v>
+        <v>0.005294444836375532</v>
       </c>
       <c r="P32" t="n">
-        <v>0.004833449354825834</v>
+        <v>0.004833449354825836</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.005297065322989855</v>
+        <v>0.005297065322989854</v>
       </c>
       <c r="R32" t="n">
         <v>0.005322210445090291</v>
       </c>
       <c r="S32" t="n">
-        <v>0.004147358783128771</v>
+        <v>0.004147358783128769</v>
       </c>
       <c r="T32" t="n">
-        <v>0.004727242463626919</v>
+        <v>0.004727242463626923</v>
       </c>
       <c r="U32" t="n">
-        <v>0.004723028497583116</v>
+        <v>0.00472302849758312</v>
       </c>
       <c r="V32" t="n">
-        <v>0.004622341960089864</v>
+        <v>0.004622341960089859</v>
       </c>
       <c r="W32" t="n">
-        <v>0.004607722790327627</v>
+        <v>0.00460772279032763</v>
       </c>
       <c r="X32" t="n">
-        <v>0.00416636520585357</v>
+        <v>0.004166365205853565</v>
       </c>
     </row>
     <row r="33">
@@ -2831,46 +2831,46 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.002600046901187731</v>
+        <v>0.00260004690118773</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002306279274723167</v>
+        <v>0.00230627927472317</v>
       </c>
       <c r="E33" t="n">
         <v>0.002799438670667367</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00246388479609888</v>
+        <v>0.002463884796098878</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002468769173826895</v>
+        <v>0.002468769173826897</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002630471649564011</v>
+        <v>0.00263047164956401</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00254655144211082</v>
+        <v>0.002546551442110823</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002233034881873</v>
+        <v>0.002233034881872999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002486916458867877</v>
+        <v>0.002486916458867875</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002476380482172507</v>
+        <v>0.002476380482172504</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002579042161881105</v>
+        <v>0.002579042161881106</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002336612499155506</v>
+        <v>0.002336612499155504</v>
       </c>
       <c r="O33" t="n">
-        <v>0.002355587829954704</v>
+        <v>0.002355587829954705</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00202037522167791</v>
+        <v>0.002020375221677911</v>
       </c>
       <c r="Q33" t="n">
         <v>0.001632528950591751</v>
@@ -2879,22 +2879,22 @@
         <v>0.001644520213521556</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001668672550912334</v>
+        <v>0.001668672550912333</v>
       </c>
       <c r="T33" t="n">
-        <v>0.001587469266484264</v>
+        <v>0.001587469266484266</v>
       </c>
       <c r="U33" t="n">
-        <v>0.001730254594187798</v>
+        <v>0.0017302545941878</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001640242565962641</v>
+        <v>0.001640242565962639</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00166426817230177</v>
+        <v>0.001664268172301771</v>
       </c>
       <c r="X33" t="n">
-        <v>0.001738370527931278</v>
+        <v>0.001738370527931276</v>
       </c>
     </row>
     <row r="34">
@@ -2907,70 +2907,70 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01855081488106518</v>
+        <v>0.01855081488106517</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01065552727165254</v>
+        <v>0.01065552727165255</v>
       </c>
       <c r="E34" t="n">
         <v>0.009780956939621851</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01152899634984669</v>
+        <v>0.01152899634984668</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01104195070932283</v>
+        <v>0.01104195070932284</v>
       </c>
       <c r="H34" t="n">
-        <v>0.008818347839144706</v>
+        <v>0.008818347839144704</v>
       </c>
       <c r="I34" t="n">
-        <v>0.009940940207141636</v>
+        <v>0.009940940207141648</v>
       </c>
       <c r="J34" t="n">
-        <v>0.009694681232449024</v>
+        <v>0.00969468123244902</v>
       </c>
       <c r="K34" t="n">
-        <v>0.008377758344591819</v>
+        <v>0.008377758344591812</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01354732189686723</v>
+        <v>0.01354732189686722</v>
       </c>
       <c r="M34" t="n">
-        <v>0.01605582766247252</v>
+        <v>0.01605582766247253</v>
       </c>
       <c r="N34" t="n">
-        <v>0.01733162616047114</v>
+        <v>0.01733162616047113</v>
       </c>
       <c r="O34" t="n">
-        <v>0.01890955816342627</v>
+        <v>0.01890955816342628</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0221613066052541</v>
+        <v>0.02216130660525411</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.02289961973851573</v>
+        <v>0.02289961973851572</v>
       </c>
       <c r="R34" t="n">
-        <v>0.02455041209692514</v>
+        <v>0.02455041209692515</v>
       </c>
       <c r="S34" t="n">
-        <v>0.02036905785676333</v>
+        <v>0.02036905785676332</v>
       </c>
       <c r="T34" t="n">
-        <v>0.01278446255016815</v>
+        <v>0.01278446255016816</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01148251134733686</v>
+        <v>0.01148251134733687</v>
       </c>
       <c r="V34" t="n">
-        <v>0.01152213688260489</v>
+        <v>0.01152213688260488</v>
       </c>
       <c r="W34" t="n">
-        <v>0.02763190915094851</v>
+        <v>0.02763190915094852</v>
       </c>
       <c r="X34" t="n">
-        <v>0.02080887713747034</v>
+        <v>0.02080887713747032</v>
       </c>
     </row>
     <row r="35">
@@ -2983,70 +2983,70 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.004675072368197259</v>
+        <v>0.004675072368197257</v>
       </c>
       <c r="D35" t="n">
-        <v>0.002625234132659127</v>
+        <v>0.00262523413265913</v>
       </c>
       <c r="E35" t="n">
         <v>0.003376584521781367</v>
       </c>
       <c r="F35" t="n">
-        <v>0.003306377273312222</v>
+        <v>0.00330637727331222</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00339225017771334</v>
+        <v>0.003392250177713343</v>
       </c>
       <c r="H35" t="n">
         <v>0.002197865382732078</v>
       </c>
       <c r="I35" t="n">
-        <v>0.003304444557469617</v>
+        <v>0.003304444557469621</v>
       </c>
       <c r="J35" t="n">
-        <v>0.003531716005268231</v>
+        <v>0.00353171600526823</v>
       </c>
       <c r="K35" t="n">
-        <v>0.003623906815298163</v>
+        <v>0.00362390681529816</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00309667760590582</v>
+        <v>0.003096677605905816</v>
       </c>
       <c r="M35" t="n">
-        <v>0.003361621584909975</v>
+        <v>0.003361621584909977</v>
       </c>
       <c r="N35" t="n">
-        <v>0.003568222878431146</v>
+        <v>0.003568222878431144</v>
       </c>
       <c r="O35" t="n">
-        <v>0.003117832052130659</v>
+        <v>0.00311783205213066</v>
       </c>
       <c r="P35" t="n">
-        <v>0.005090274910113061</v>
+        <v>0.005090274910113063</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.004923518772318099</v>
+        <v>0.004923518772318098</v>
       </c>
       <c r="R35" t="n">
         <v>0.004735506759584078</v>
       </c>
       <c r="S35" t="n">
-        <v>0.004858789620625786</v>
+        <v>0.004858789620625783</v>
       </c>
       <c r="T35" t="n">
-        <v>0.005410233887159183</v>
+        <v>0.005410233887159189</v>
       </c>
       <c r="U35" t="n">
-        <v>0.005083757202042067</v>
+        <v>0.005083757202042072</v>
       </c>
       <c r="V35" t="n">
-        <v>0.005485549398790005</v>
+        <v>0.00548554939879</v>
       </c>
       <c r="W35" t="n">
-        <v>0.004815876884153697</v>
+        <v>0.0048158768841537</v>
       </c>
       <c r="X35" t="n">
-        <v>0.005442647634666496</v>
+        <v>0.00544264763466649</v>
       </c>
     </row>
   </sheetData>
